--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486448_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486448_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7833</v>
+        <v>4.6702</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2905</v>
+        <v>4.8847</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5072</v>
+        <v>-0.2145</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0792</v>
+        <v>2.7024</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3303</v>
+        <v>0.3772</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.251</v>
+        <v>2.3252</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7353</v>
+        <v>4.3896</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5441</v>
+        <v>1.5575</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1912</v>
+        <v>2.8321</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6561</v>
+        <v>-1.6872</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2138</v>
+        <v>-1.1803</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4423</v>
+        <v>-0.5068</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.442</v>
+        <v>0.2277</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4252</v>
+        <v>0.4951</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0168</v>
+        <v>-0.2674</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.646</v>
+        <v>3.6495</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9221</v>
+        <v>6.465</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2761</v>
+        <v>-2.8154</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7024</v>
+        <v>3.0792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3772</v>
+        <v>3.3303</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3252</v>
+        <v>-0.251</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3896</v>
+        <v>4.7353</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5575</v>
+        <v>4.5441</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8321</v>
+        <v>0.1912</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6872</v>
+        <v>-1.6561</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1803</v>
+        <v>-1.2138</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5068</v>
+        <v>-0.4423</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7965</v>
+        <v>0.3082</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4675</v>
+        <v>0.5997</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.329</v>
+        <v>-0.2914</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2038</v>
+        <v>2.7645</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5445</v>
+        <v>2.321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6593</v>
+        <v>0.4435</v>
       </c>
       <c r="G4" t="n">
         <v>1.6246</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8391</v>
+        <v>0.3999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5736</v>
+        <v>0.3578</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5744</v>
+        <v>2.3431</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2314</v>
+        <v>-0.2156</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3429</v>
+        <v>2.5587</v>
       </c>
       <c r="G5" t="n">
         <v>2.487</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.1439</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4711</v>
+        <v>0.024</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3837</v>
+        <v>-0.1679</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7347</v>
+        <v>0.9081</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2443</v>
+        <v>2.3561</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5096</v>
+        <v>-1.448</v>
       </c>
       <c r="G6" t="n">
         <v>2.3652</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7604</v>
+        <v>-0.587</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0649</v>
+        <v>0.0469</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6956</v>
+        <v>-0.6339</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2419</v>
+        <v>-0.4479</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1958</v>
+        <v>1.4135</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9539</v>
+        <v>-1.8614</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0391</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4762</v>
+        <v>-0.2136</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6682</v>
+        <v>-0.1142</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1919</v>
+        <v>-0.0994</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3969</v>
+        <v>-2.2966</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3578</v>
+        <v>-2.1343</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.039</v>
+        <v>-0.1623</v>
       </c>
       <c r="G8" t="n">
         <v>-3.165</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6218</v>
+        <v>-0.5215</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2002</v>
+        <v>0.0769</v>
       </c>
       <c r="V8" t="n">
         <v>2.2599</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2374</v>
+        <v>-2.7676</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1484</v>
+        <v>-1.0835</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0891</v>
+        <v>-1.6841</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1742</v>
+        <v>-0.6589</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7877</v>
+        <v>-2.2231</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3865</v>
+        <v>1.5642</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5319</v>
+        <v>1.2259</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3989</v>
+        <v>-0.9942</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1331</v>
+        <v>2.2201</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3577</v>
+        <v>-1.8847</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6111</v>
+        <v>-1.2289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2534</v>
+        <v>-0.6558</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8256</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6165</v>
+        <v>0.5203</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2091</v>
+        <v>0.0255</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8902</v>
+        <v>0.3904</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8902</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5876</v>
+        <v>-2.9022</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9343</v>
+        <v>-1.8131</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6533</v>
+        <v>-1.0891</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6589</v>
+        <v>-1.1742</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2231</v>
+        <v>-0.7877</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5642</v>
+        <v>-0.3865</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2259</v>
+        <v>-1.5319</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9942</v>
+        <v>-1.3989</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2201</v>
+        <v>-0.1331</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8847</v>
+        <v>0.3577</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2289</v>
+        <v>0.6111</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6558</v>
+        <v>-0.2534</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0451</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2741</v>
+        <v>-0.4903</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3305</v>
+        <v>-0.2812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0564</v>
+        <v>-0.2091</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3904</v>
+        <v>-1.8902</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1486</v>
+        <v>-3.6023</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2514</v>
+        <v>-2.7359</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8972</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>2.3095</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1525</v>
+        <v>0.3939</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>0.0361</v>
       </c>
       <c r="U11" t="n">
-        <v>0.327</v>
+        <v>0.3578</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5204</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7746</v>
+        <v>-6.9373</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2937</v>
+        <v>-3.6723</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4809</v>
+        <v>-3.2651</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8055</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4659</v>
+        <v>0.3031</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9542</v>
+        <v>0.5756</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4883</v>
+        <v>-0.2725</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.960999999999999</v>
+        <v>-4.618499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.443</v>
+        <v>5.785599999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-10.4041</v>
@@ -1468,10 +1468,10 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1203</v>
+        <v>0.2224000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0034</v>
+        <v>1.346</v>
       </c>
       <c r="U13" t="n">
         <v>-1.1236</v>
@@ -1483,7 +1483,7 @@
         <v>5.4753</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.516199999999998</v>
+        <v>-8.516200000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1756</v>
+        <v>6.8872</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2467</v>
+        <v>5.4702</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9288999999999999</v>
+        <v>1.417</v>
       </c>
       <c r="G14" t="n">
         <v>4.0124</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2294</v>
+        <v>0.4822</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3257</v>
+        <v>0.5492</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5551</v>
+        <v>-0.067</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3204</v>
+        <v>4.2087</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6026</v>
+        <v>5.4909</v>
       </c>
       <c r="F15" t="n">
         <v>-1.2822</v>
@@ -1624,10 +1624,10 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.274</v>
+        <v>-0.3857</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2824</v>
+        <v>-0.3941</v>
       </c>
       <c r="U15" t="n">
         <v>0.008399999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0967</v>
+        <v>1.8006</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9249</v>
+        <v>1.6956</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1718</v>
+        <v>0.105</v>
       </c>
       <c r="G16" t="n">
         <v>2.656</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9627</v>
+        <v>0.6666</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8242</v>
+        <v>0.5948</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1385</v>
+        <v>0.0718</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3045</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3098</v>
+        <v>1.06</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4318</v>
+        <v>2.8788</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.122</v>
+        <v>-1.8188</v>
       </c>
       <c r="G17" t="n">
         <v>-2.0528</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6373</v>
+        <v>-0.8872</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7469</v>
+        <v>-0.4437</v>
       </c>
       <c r="V17" t="n">
         <v>2.2599</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0108</v>
+        <v>0.0416</v>
       </c>
       <c r="E18" t="n">
         <v>0.0063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0046</v>
+        <v>0.0354</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0097</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.197</v>
+        <v>-0.1661</v>
       </c>
       <c r="T18" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2934</v>
+        <v>-0.2087</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6024</v>
+        <v>0.3789</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8959</v>
+        <v>-0.5876</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6155</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3221</v>
+        <v>0.4068</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0565</v>
+        <v>0.3647</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5569</v>
+        <v>-0.2233</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.253</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.378</v>
+        <v>-0.4763</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9782</v>
+        <v>-0.8617</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0243</v>
+        <v>0.2858</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0025</v>
+        <v>-1.1475</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9855</v>
+        <v>0.0547</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3536</v>
+        <v>0.0547</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6319</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9637</v>
+        <v>-0.9164</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3293</v>
+        <v>0.2311</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6344</v>
+        <v>-1.1475</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4487</v>
+        <v>0.2034</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0769</v>
+        <v>0.1983</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3718</v>
+        <v>0.0051</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.651</v>
+        <v>-0.4566</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0822</v>
+        <v>1.0446</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5688</v>
+        <v>-1.5013</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8617</v>
+        <v>-0.9782</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2858</v>
+        <v>0.0243</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1475</v>
+        <v>-1.0025</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0547</v>
+        <v>1.9855</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0547</v>
+        <v>1.3536</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6319</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9164</v>
+        <v>-2.9637</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2311</v>
+        <v>-1.3293</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1475</v>
+        <v>-1.6344</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2244</v>
+        <v>-0.3485</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.137</v>
+        <v>0.1466</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.4951</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2946</v>
+        <v>-1.4637</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8467</v>
+        <v>-2.7477</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5522</v>
+        <v>1.2839</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3192</v>
+        <v>-2.7615</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0929</v>
+        <v>-1.767</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2263</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2409</v>
+        <v>-2.7542</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.013</v>
+        <v>-2.1622</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2279</v>
+        <v>-0.5921</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0783</v>
+        <v>-0.0073</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0799</v>
+        <v>0.3951</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.4024</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1546</v>
+        <v>-0.2025</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4817</v>
+        <v>-0.1887</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.0138</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6602</v>
+        <v>-1.5449</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6359</v>
+        <v>-0.3881</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9757</v>
+        <v>-1.1568</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7615</v>
+        <v>-0.6274</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.767</v>
+        <v>-0.4442</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-0.1833</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7542</v>
+        <v>1.3393</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1622</v>
+        <v>-0.3253</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5921</v>
+        <v>1.6647</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0073</v>
+        <v>-1.9668</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3951</v>
+        <v>-0.1188</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4024</v>
+        <v>-1.8479</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.399</v>
+        <v>-0.0475</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0769</v>
+        <v>0.2524</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3221</v>
+        <v>-0.2998</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7349</v>
+        <v>-1.8979</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2729</v>
+        <v>-0.9376</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.462</v>
+        <v>-0.9603</v>
       </c>
       <c r="G24" t="n">
         <v>1.0205</v>
@@ -2326,13 +2326,13 @@
         <v>2.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3544</v>
+        <v>0.1914</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4879</v>
+        <v>-0.1526</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.344</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9347</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7614</v>
+        <v>-2.4969</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.394</v>
+        <v>-2.7408</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3674</v>
+        <v>0.2439</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6274</v>
+        <v>-4.3192</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4442</v>
+        <v>-3.0929</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1833</v>
+        <v>-1.2263</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3393</v>
+        <v>-2.2409</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3253</v>
+        <v>-2.013</v>
       </c>
       <c r="L25" t="n">
-        <v>1.6647</v>
+        <v>-0.2279</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9668</v>
+        <v>-2.0783</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1188</v>
+        <v>-1.0799</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8479</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.87</v>
+        <v>0.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R25" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2639</v>
+        <v>0.9523</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5105</v>
+        <v>0.3647</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.960900000000001</v>
+        <v>5.706100000000001</v>
       </c>
       <c r="E26" t="n">
         <v>10.4041</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.4431</v>
+        <v>-4.698099999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.725199999999999</v>
+        <v>-4.7252</v>
       </c>
       <c r="H26" t="n">
-        <v>3.8927</v>
+        <v>3.892699999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-8.618</v>
@@ -2473,22 +2473,22 @@
         <v>-12.8414</v>
       </c>
       <c r="P26" t="n">
-        <v>6.525199999999999</v>
+        <v>6.525200000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.787700000000001</v>
+        <v>-9.787699999999999</v>
       </c>
       <c r="R26" t="n">
         <v>16.3131</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1200999999999997</v>
+        <v>0.8652000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>1.1237</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0038</v>
+        <v>-0.2583000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>3.0408</v>
